--- a/artfynd/A 38890-2024 artfynd.xlsx
+++ b/artfynd/A 38890-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74799338</v>
+        <v>194011</v>
       </c>
       <c r="B2" t="n">
-        <v>93021</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,12 +700,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(With.) Myrin</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,20 +718,19 @@
           <t>utan kapsel</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Horgeboda (DcUE18), delpop. 9, Sm</t>
+          <t>Horgeboda, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475841.8310982897</v>
+        <v>475803</v>
       </c>
       <c r="R2" t="n">
-        <v>6269330.838024204</v>
+        <v>6269381</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,27 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Arten förekommer inom 2 m2</t>
+          <t>5 tussar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,21 +773,22 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Vattenstrand</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>sjöstrand</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>2</v>
+          <t>grund strand med rikligt med pors</t>
+        </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2 substratenheter # sten</t>
+          <t>sten i strandzonen.från vattenytan och 2 dm upp. I skyddat läge.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,10 +799,411 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74799338</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>530</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Horgeboda (DcUE18), delpop. 9, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>475842</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6269331</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västra Torsås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Arten förekommer inom 2 m2</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2 substratenheter # sten</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Per Darell, Martin Andersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>74799339</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>530</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Horgeboda (DcUE18), delpop. 8, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>475842</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6269365</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Torsås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Arten förekommer inom 1 m2</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sten</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Darell, Martin Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>74799340</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>530</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Horgeboda (DcUE18), delpop. 7, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>475816</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6269375</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västra Torsås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Arten förekommer inom 1 m2</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sten</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Darell, Martin Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
         </is>

--- a/artfynd/A 38890-2024 artfynd.xlsx
+++ b/artfynd/A 38890-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/194011</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -938,6 +948,11 @@
           <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74799338</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1073,6 +1088,11 @@
           <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74799339</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1208,8 +1228,19 @@
           <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74799340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>